--- a/AAII_Financials/Quarterly/FERG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FERG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>FERG</t>
   </si>
@@ -656,326 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
-        <v>45688</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44043</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8751000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7472000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8169000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8497000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>8363000</v>
+      </c>
+      <c r="I8" s="3">
         <v>7621000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>7213000</v>
       </c>
-      <c r="I8" s="3">
-        <v>6872000</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7772000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7308000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6673000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7708000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7838000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7140000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6825000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7931000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7971000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7284000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6508000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6803000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12483000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5916000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10309000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5372000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10047000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6039000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5154000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5663000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5803000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>5750000</v>
+      </c>
+      <c r="I9" s="3">
         <v>5262000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>4997000</v>
       </c>
-      <c r="I9" s="3">
-        <v>4830000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5432000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5076000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4644000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5377000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5436000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5000000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4763000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5510000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5536000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5079000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4519000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4676000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8596000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>14432000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>14724000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2712000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2318000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2506000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2694000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>2613000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2359000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2216000</v>
       </c>
-      <c r="I10" s="3">
-        <v>2042000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2340000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2232000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2029000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2331000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2402000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2140000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2062000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2421000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2435000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2205000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1989000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2127000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3887000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>-4123000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-4677000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1017,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1076,8 +1092,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1150,50 +1169,53 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>7000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="I14" s="3">
         <v>70000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>51000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>12000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>-2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>127000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1209,61 +1231,64 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>7000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>4000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>165000</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E15" s="3">
         <v>97000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>94000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>97000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>96000</v>
+      </c>
+      <c r="I15" s="3">
         <v>94000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>93000</v>
       </c>
-      <c r="I15" s="3">
-        <v>92000</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>90000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>85000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>83000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>80000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>78000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>81000</v>
       </c>
       <c r="P15" s="3">
         <v>81000</v>
@@ -1272,34 +1297,37 @@
         <v>81000</v>
       </c>
       <c r="R15" s="3">
+        <v>81000</v>
+      </c>
+      <c r="S15" s="3">
         <v>77000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>78000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>72000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>74000</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3">
         <v>141000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1323,156 +1351,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7862000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6864000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7403000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7568000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>7499000</v>
+      </c>
+      <c r="I17" s="3">
         <v>6948000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6658000</v>
       </c>
-      <c r="I17" s="3">
-        <v>6464000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7111000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6674000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6199000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6972000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7048000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6519000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6280000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7100000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7157000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6572000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5953000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6064000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11260000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>9540000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>9310000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>889000</v>
+      </c>
+      <c r="E18" s="3">
         <v>608000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>766000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>929000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>864000</v>
+      </c>
+      <c r="I18" s="3">
         <v>673000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>555000</v>
       </c>
-      <c r="I18" s="3">
-        <v>408000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>661000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>634000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>474000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>736000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>790000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>621000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>545000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>831000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>814000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>712000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>555000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>739000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1223000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>769000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>737000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1499,142 +1534,146 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>-11000</v>
       </c>
-      <c r="I20" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-39000</v>
       </c>
       <c r="R20" s="3">
         <v>-39000</v>
       </c>
       <c r="S20" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="T20" s="3">
         <v>-22000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-28000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>27000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>999000</v>
+      </c>
+      <c r="E21" s="3">
         <v>704000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>852000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1026000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>960000</v>
+      </c>
+      <c r="I21" s="3">
         <v>767000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>659000</v>
       </c>
-      <c r="I21" s="3">
-        <v>510000</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>760000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>721000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>560000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>816000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>854000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>703000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>623000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>572000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>852000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>768000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>604000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>785000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1647,53 +1686,56 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E22" s="3">
         <v>45000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>46000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>49000</v>
+      </c>
+      <c r="I22" s="3">
         <v>46000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>46000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>48000</v>
       </c>
       <c r="J22" s="3">
         <v>46000</v>
       </c>
       <c r="K22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="L22" s="3">
         <v>43000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>45000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>48000</v>
       </c>
       <c r="O22" s="3">
         <v>48000</v>
       </c>
       <c r="P22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>47000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1706,171 +1748,180 @@
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>69000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>76000</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>846000</v>
+      </c>
+      <c r="E23" s="3">
         <v>560000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>712000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>872000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>790000</v>
+      </c>
+      <c r="I23" s="3">
         <v>557000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>469000</v>
       </c>
-      <c r="I23" s="3">
-        <v>370000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>624000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>581000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>433000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>691000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>730000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>447000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>495000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>792000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>775000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>690000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>532000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>711000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1152000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>720000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>664000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E24" s="3">
         <v>146000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>142000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>172000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>156000</v>
+      </c>
+      <c r="I24" s="3">
         <v>147000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>124000</v>
       </c>
-      <c r="I24" s="3">
-        <v>94000</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>154000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>138000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>111000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>172000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>146000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>111000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>121000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>197000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>193000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>144000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>96000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>176000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>109000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>127000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1943,156 +1994,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E26" s="3">
         <v>414000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>570000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>634000</v>
+      </c>
+      <c r="I26" s="3">
         <v>410000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>345000</v>
       </c>
-      <c r="I26" s="3">
-        <v>276000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>470000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>443000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>322000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>519000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>584000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>336000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>374000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>595000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>582000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>546000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>436000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>535000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1043000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>593000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>517000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E27" s="3">
         <v>414000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>570000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>634000</v>
+      </c>
+      <c r="I27" s="3">
         <v>410000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>345000</v>
       </c>
-      <c r="I27" s="3">
-        <v>276000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>470000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>443000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>322000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>519000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>584000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>336000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>374000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>595000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>582000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>546000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>436000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>535000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1043000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>593000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>517000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2165,8 +2225,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2213,34 +2276,37 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-2000</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>25000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>7000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-313000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2313,8 +2379,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2387,156 +2456,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>11000</v>
       </c>
-      <c r="I32" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>-14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>39000</v>
       </c>
       <c r="R32" s="3">
         <v>39000</v>
       </c>
       <c r="S32" s="3">
+        <v>39000</v>
+      </c>
+      <c r="T32" s="3">
         <v>22000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>28000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E33" s="3">
         <v>414000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>570000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>700000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>634000</v>
+      </c>
+      <c r="I33" s="3">
         <v>410000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>345000</v>
       </c>
-      <c r="I33" s="3">
-        <v>276000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>470000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>443000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>322000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>519000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>584000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>336000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>374000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>595000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>580000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>546000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>436000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>560000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1050000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>280000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>494000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2609,161 +2687,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E35" s="3">
         <v>414000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>570000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>700000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>634000</v>
+      </c>
+      <c r="I35" s="3">
         <v>410000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>345000</v>
       </c>
-      <c r="I35" s="3">
-        <v>276000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>470000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>443000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>322000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>519000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>584000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>336000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>374000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>595000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>580000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>546000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>436000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>560000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1050000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>280000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>494000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
-        <v>45688</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44043</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2790,8 +2877,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2818,82 +2906,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E41" s="3">
         <v>820000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>526000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>674000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3">
         <v>519000</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I41" s="3">
-        <v>764000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>601000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>691000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>639000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>743000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>601000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>625000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>597000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>771000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>1160000</v>
       </c>
       <c r="S41" s="3">
         <v>1160000</v>
       </c>
       <c r="T41" s="3">
+        <v>1160000</v>
+      </c>
+      <c r="U41" s="3">
         <v>828000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2166000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1335000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1723000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2115000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>775000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2958,164 +3050,173 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="3">
         <v>9000</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4255000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3669000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3807000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4435000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>3748000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I43" s="3">
-        <v>3200000</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>3642000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3532000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3092000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3600000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3597000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3382000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3166000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3610000</v>
-      </c>
-      <c r="R43" s="3">
-        <v>3431000</v>
       </c>
       <c r="S43" s="3">
         <v>3431000</v>
       </c>
       <c r="T43" s="3">
+        <v>3431000</v>
+      </c>
+      <c r="U43" s="3">
         <v>2931000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3066000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3335000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2622000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3042000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2984000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5101000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4676000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4613000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4492000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3">
         <v>4548000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I44" s="3">
-        <v>4273000</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
         <v>4393000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4115000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3968000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4106000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3898000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4089000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4173000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4333000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>4113000</v>
       </c>
       <c r="S44" s="3">
         <v>4113000</v>
       </c>
       <c r="T44" s="3">
+        <v>4113000</v>
+      </c>
+      <c r="U44" s="3">
         <v>3776000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3660000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3426000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3011000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2880000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2970000</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3123,147 +3224,153 @@
         <v>39000</v>
       </c>
       <c r="E45" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F45" s="3">
         <v>56000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>71000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>44000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>26000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
+        <v>30000</v>
+      </c>
+      <c r="M45" s="3">
         <v>26000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>30000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>26000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>28000</v>
       </c>
       <c r="N45" s="3">
         <v>28000</v>
       </c>
       <c r="O45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="P45" s="3">
         <v>30000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>837000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>824000</v>
       </c>
       <c r="S45" s="3">
         <v>824000</v>
       </c>
       <c r="T45" s="3">
+        <v>824000</v>
+      </c>
+      <c r="U45" s="3">
         <v>796000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>780000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>22000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11027000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10165000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10027000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10146000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3">
         <v>9776000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I46" s="3">
-        <v>9225000</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>9625000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9314000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8616000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9470000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9077000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8909000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8768000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9551000</v>
-      </c>
-      <c r="R46" s="3">
-        <v>9528000</v>
       </c>
       <c r="S46" s="3">
         <v>9528000</v>
       </c>
       <c r="T46" s="3">
+        <v>9528000</v>
+      </c>
+      <c r="U46" s="3">
         <v>8331000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9672000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8101000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7357000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8057000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6760000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3306,8 +3413,8 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3318,174 +3425,183 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>451000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>414000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>393000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>419000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3938000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3824000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3727000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3609000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>3510000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3445000</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>3390000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3203000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3198000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3151000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3069000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2863000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2776000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2576000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>2506000</v>
       </c>
       <c r="S48" s="3">
         <v>2506000</v>
       </c>
       <c r="T48" s="3">
+        <v>2506000</v>
+      </c>
+      <c r="U48" s="3">
         <v>2471000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2418000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2200000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2224000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2500000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2614000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3663000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3134000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3168000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3190000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>3177000</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3060000</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>3083000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3092000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3019000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3002000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3024000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2751000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2893000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2830000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>2563000</v>
       </c>
       <c r="S49" s="3">
         <v>2563000</v>
       </c>
       <c r="T49" s="3">
+        <v>2563000</v>
+      </c>
+      <c r="U49" s="3">
         <v>2551000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1883000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2303000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2279000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2242000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2142000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3558,8 +3674,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3632,82 +3751,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E52" s="3">
         <v>541000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>636000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>559000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
         <v>605000</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3">
-        <v>612000</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>574000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>543000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>554000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>496000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>524000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>576000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>565000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>704000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>709000</v>
       </c>
       <c r="S52" s="3">
         <v>709000</v>
       </c>
       <c r="T52" s="3">
+        <v>709000</v>
+      </c>
+      <c r="U52" s="3">
         <v>747000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1341000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>430000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>205000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>264000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>285000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3780,82 +3905,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19303000</v>
+      </c>
+      <c r="E54" s="3">
         <v>17789000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17694000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17729000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3">
         <v>17265000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I54" s="3">
-        <v>16530000</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>16858000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16458000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15687000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16418000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15994000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15364000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15216000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15661000</v>
-      </c>
-      <c r="R54" s="3">
-        <v>15306000</v>
       </c>
       <c r="S54" s="3">
         <v>15306000</v>
       </c>
       <c r="T54" s="3">
+        <v>15306000</v>
+      </c>
+      <c r="U54" s="3">
         <v>14100000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15314000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13485000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12479000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13456000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12220000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3882,8 +4013,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3910,452 +4042,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3677000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3468000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3577000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
         <v>3775000</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3027000</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>3430000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3638000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2985000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3555000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3408000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3297000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3155000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3607000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>3630000</v>
       </c>
       <c r="S57" s="3">
         <v>3630000</v>
       </c>
       <c r="T57" s="3">
+        <v>3630000</v>
+      </c>
+      <c r="U57" s="3">
         <v>3063000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3213000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4022000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3118000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3591000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3120000</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>925000</v>
+      </c>
+      <c r="E58" s="3">
         <v>613000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>461000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>847000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>828000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>816000</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>956000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>532000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>529000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>428000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>421000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>398000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>391000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>250000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>300000</v>
       </c>
       <c r="S58" s="3">
         <v>300000</v>
       </c>
       <c r="T58" s="3">
+        <v>300000</v>
+      </c>
+      <c r="U58" s="3">
         <v>296000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>446000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>476000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>812000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>987000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1392000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1408000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1410000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1604000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
         <v>1368000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1214000</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>1353000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1359000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1274000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1554000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1430000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1368000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1942000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2190000</v>
       </c>
       <c r="S59" s="3">
         <v>2190000</v>
       </c>
       <c r="T59" s="3">
+        <v>2190000</v>
+      </c>
+      <c r="U59" s="3">
         <v>1645000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3192000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>375000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>345000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>346000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>328000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6377000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5698000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5339000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6028000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3">
         <v>5971000</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I60" s="3">
-        <v>5057000</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>5739000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5529000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4788000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5537000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5429000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5125000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4914000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5799000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>6120000</v>
       </c>
       <c r="S60" s="3">
         <v>6120000</v>
       </c>
       <c r="T60" s="3">
+        <v>6120000</v>
+      </c>
+      <c r="U60" s="3">
         <v>5004000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6405000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4843000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3939000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4749000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4435000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5962000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5468000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5558000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5119000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>5001000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>5205000</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>4682000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4673000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4760000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4835000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4837000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4834000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4897000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3679000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>3221000</v>
       </c>
       <c r="S61" s="3">
         <v>3221000</v>
       </c>
       <c r="T61" s="3">
+        <v>3221000</v>
+      </c>
+      <c r="U61" s="3">
         <v>2749000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2271000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3355000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3521000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3709000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3199000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>763000</v>
+      </c>
+      <c r="E62" s="3">
         <v>749000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>741000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>750000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3">
         <v>762000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3">
-        <v>779000</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>782000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>734000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>721000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>686000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>691000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>684000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>680000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1518000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1462000</v>
       </c>
       <c r="S62" s="3">
         <v>1462000</v>
       </c>
       <c r="T62" s="3">
+        <v>1462000</v>
+      </c>
+      <c r="U62" s="3">
         <v>1502000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1481000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>477000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>526000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>627000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>481000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4428,8 +4579,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4502,8 +4656,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4576,82 +4733,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13102000</v>
+      </c>
+      <c r="E66" s="3">
         <v>11915000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11638000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11897000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3">
         <v>11734000</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I66" s="3">
-        <v>11041000</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>11203000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10936000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10269000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11058000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10957000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10643000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10491000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10996000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>10803000</v>
       </c>
       <c r="S66" s="3">
         <v>10803000</v>
       </c>
       <c r="T66" s="3">
+        <v>10803000</v>
+      </c>
+      <c r="U66" s="3">
         <v>9255000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10157000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8675000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7986000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9085000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8115000</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4678,8 +4841,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4752,8 +4916,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4826,8 +4993,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4900,8 +5070,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4974,82 +5147,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7889000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7403000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7117000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6776000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3">
         <v>6241000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3">
-        <v>5998000</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>5889000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9301000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9018000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8858000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8557000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8128000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7945000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7594000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>6542000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>6158000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4454000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5553000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9260000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5122,8 +5301,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5196,8 +5378,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5270,82 +5455,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6201000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5874000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6056000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5832000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3">
         <v>5531000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="3">
-        <v>5489000</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>5655000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5522000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5418000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5360000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5037000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4721000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4725000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4665000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>4503000</v>
       </c>
       <c r="S76" s="3">
         <v>4503000</v>
       </c>
       <c r="T76" s="3">
+        <v>4503000</v>
+      </c>
+      <c r="U76" s="3">
         <v>4845000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5157000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4810000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4493000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4371000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4105000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5418,161 +5609,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
-        <v>45688</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44043</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E81" s="3">
         <v>414000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>570000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>700000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>634000</v>
+      </c>
+      <c r="I81" s="3">
         <v>410000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>345000</v>
       </c>
-      <c r="I81" s="3">
-        <v>276000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>470000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>443000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>322000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>519000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>584000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>336000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>374000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>595000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>580000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>546000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>436000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>560000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1050000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>280000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>494000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5599,34 +5799,35 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F83" s="3">
         <v>54000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>53000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>52000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>20000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>48000</v>
       </c>
-      <c r="I83" s="3">
-        <v>48000</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>48000</v>
       </c>
       <c r="L83" s="3">
         <v>48000</v>
@@ -5635,32 +5836,32 @@
         <v>48000</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>48000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>56000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-220000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>77000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>78000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>72000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>74000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5673,8 +5874,11 @@
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5747,8 +5951,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5821,8 +6028,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5895,8 +6105,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5969,8 +6182,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6043,68 +6259,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E89" s="3">
         <v>772000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>430000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>541000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>249000</v>
+      </c>
+      <c r="I89" s="3">
         <v>682000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>874000</v>
       </c>
-      <c r="I89" s="3">
-        <v>340000</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>345000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>644000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>306000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>557000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>921000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>631000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>673000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-651000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>468000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>452000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>242000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6117,8 +6336,11 @@
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6145,71 +6367,72 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-92000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-118000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-70000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-73000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-81000</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-77000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-101000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-91000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-80000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-119000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-147000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-95000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-73000</v>
       </c>
       <c r="S91" s="3">
         <v>-73000</v>
       </c>
       <c r="T91" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-71000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-51000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-114000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6219,8 +6442,11 @@
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6293,8 +6519,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6367,68 +6596,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-706000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-94000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-132000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-79000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-272000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-211000</v>
       </c>
-      <c r="I94" s="3">
-        <v>-93000</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-99000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-187000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-135000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-96000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-511000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-118000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-321000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>818000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-471000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-111000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-260000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6441,8 +6673,11 @@
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6469,59 +6704,60 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E96" s="3">
         <v>174000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>164000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>165000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
+        <v>164000</v>
+      </c>
+      <c r="I96" s="3">
         <v>166000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>166000</v>
       </c>
-      <c r="I96" s="3">
-        <v>158000</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>160000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>153000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>152000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>154000</v>
       </c>
       <c r="O96" s="3">
         <v>154000</v>
       </c>
       <c r="P96" s="3">
+        <v>154000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>403000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-174000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -6543,8 +6779,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6617,8 +6856,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6691,8 +6933,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6765,68 +7010,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-413000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-448000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-311000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-311000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-686000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-814000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-75000</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-214000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-398000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-284000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-313000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-418000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-483000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-387000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>225000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-373000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1293000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>930000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6839,68 +7087,71 @@
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F101" s="3">
         <v>9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>27000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>32000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-21000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6000</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
@@ -6913,68 +7164,71 @@
       <c r="Z101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-369000</v>
+      </c>
+      <c r="E102" s="3">
         <v>263000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-152000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>151000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-187000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-259000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-142000</v>
       </c>
-      <c r="I102" s="3">
-        <v>161000</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>51000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-104000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>139000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>424000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-385000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>328000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1331000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>831000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6985,6 +7239,9 @@
         <v>5</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
